--- a/auto_script.xlsx
+++ b/auto_script.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_Project_EMIC\7_ToolTest\BoardTest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Firmware_TNT\6_DA_2026\BoardTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6DDC10-CA2F-4C78-95FE-1EEEFD705DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -66,7 +65,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -417,14 +416,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
     <col min="7" max="7" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/auto_script.xlsx
+++ b/auto_script.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Firmware_TNT\6_DA_2026\BoardTest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_Project_EMIC\7_ToolTest\BoardTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E5F9390-1C26-44EF-B9F7-EECD52739CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>STT</t>
   </si>
@@ -60,13 +61,25 @@
   </si>
   <si>
     <t>hex array</t>
+  </si>
+  <si>
+    <t>Type pack</t>
+  </si>
+  <si>
+    <t>Len Payload</t>
+  </si>
+  <si>
+    <t>Param ID</t>
+  </si>
+  <si>
+    <t>Param</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +92,21 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -122,11 +150,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -137,6 +162,10 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,179 +445,237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A3:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="7" width="17.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="I3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="J3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="K3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4">
+      <c r="I4" s="3">
         <v>2649000043</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="b">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="4">
+      <c r="I5" s="3">
         <v>2649000043</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
